--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-performer.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-performer.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T15:26:54+00:00</t>
+    <t>2025-01-23T13:26:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-performer.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-performer.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-23T13:26:37+00:00</t>
+    <t>2025-01-24T17:22:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-performer.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-performer.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-24T17:22:23+00:00</t>
+    <t>2025-01-29T14:25:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-performer.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-performer.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-29T14:25:50+00:00</t>
+    <t>2025-01-29T15:50:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-performer.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-performer.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-29T15:50:40+00:00</t>
+    <t>2025-01-30T15:03:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-performer.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-performer.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-30T15:03:39+00:00</t>
+    <t>2025-01-31T08:45:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-performer.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-performer.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-31T08:45:39+00:00</t>
+    <t>2025-02-18T10:06:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-performer.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-performer.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1442" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1609" uniqueCount="228">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T10:06:11+00:00</t>
+    <t>2025-02-18T11:00:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Performer est l'exécutant de l’évènement documenté. Il est obligatoire et son attribut nullFlavor interdit pour l’évènement documenté principal.</t>
+    <t>L'élément de l'en-tête du CDA performer permet de représenter l'exécutant de l’évènement documenté. Il est obligatoire et son attribut nullFlavor interdit pour l’évènement documenté principal.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -469,7 +469,40 @@
     <t>Performer1.assignedEntity.id</t>
   </si>
   <si>
+    <t>Identifiant du responsable</t>
+  </si>
+  <si>
     <t>AssignedEntity.id</t>
+  </si>
+  <si>
+    <t>Performer1.assignedEntity.id.nullFlavor</t>
+  </si>
+  <si>
+    <t>Performer1.assignedEntity.id.assigningAuthorityName</t>
+  </si>
+  <si>
+    <t>Performer1.assignedEntity.id.displayable</t>
+  </si>
+  <si>
+    <t>Performer1.assignedEntity.id.root</t>
+  </si>
+  <si>
+    <t>- Pour un professionnel : '1.2.250.1.71.4.2.1'
+- Pour le patient/usager : OID de l'autorité d'affectation de l'INS
+- Pour un système de structure : '1.2.250.1.71.4.2.1' 
+- Pour un SNR : OID de l'éditeur 
+- Pour le DP : '1.2.250.1.71.4.2.1'</t>
+  </si>
+  <si>
+    <t>A unique identifier that guarantees the global uniqueness of the instance identifier. The root alone may be the entire instance identifier.</t>
+  </si>
+  <si>
+    <t>Performer1.assignedEntity.id.extension</t>
+  </si>
+  <si>
+    <t>Valeur de l’identifiant.
+- Pour le PS, valeur de PS_IdNat (voir CI-SIS_ANX_SOURCES-DONNEES-PERSONNES-STRUCTURES).
+- Pour le patient/usager, valeur de l'INS du patient/usager.</t>
   </si>
   <si>
     <t>Performer1.assignedEntity.sdtcIdentifiedBy</t>
@@ -485,6 +518,9 @@
     <t>Performer1.assignedEntity.code</t>
   </si>
   <si>
+    <t>Profession ou rôle du responsable</t>
+  </si>
+  <si>
     <t>https://mos.esante.gouv.fr/NOS/JDV_J01-XdsAuthorSpecialty-CISIS/FHIR/JDV-J01-XdsAuthorSpecialty-CISIS</t>
   </si>
   <si>
@@ -628,6 +664,9 @@
 </t>
   </si>
   <si>
+    <t>Adresse géopostale</t>
+  </si>
+  <si>
     <t>AssignedEntity.addr</t>
   </si>
   <si>
@@ -638,6 +677,9 @@
 </t>
   </si>
   <si>
+    <t>Coordonnées télécom</t>
+  </si>
+  <si>
     <t>AssignedEntity.telecom</t>
   </si>
   <si>
@@ -648,6 +690,13 @@
 </t>
   </si>
   <si>
+    <t>Personne physique : 
+- Obligatoire pour un professionnel 
+- Obligatoire pour un patient/usager 
+- Non utilisé pour un SNR 
+- Non utilisé pour le DP</t>
+  </si>
+  <si>
     <t>AssignedEntity.assignedPerson</t>
   </si>
   <si>
@@ -656,6 +705,11 @@
   <si>
     <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/Organization {https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-core-represented-organization}
 </t>
+  </si>
+  <si>
+    <t>Structure de rattachement :
+- Pour un PS : Organisation pour le compte de laquelle intervient le PS.
+- Pour un patient : seul l'élément standardIndustryClassCode est renseigné (cas particulier des documents d'expression personnelle du patient).</t>
   </si>
   <si>
     <t>AssignedEntity.representedOrganization</t>
@@ -976,7 +1030,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK45"/>
+  <dimension ref="A1:AK50"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="55.046875" customWidth="true" bestFit="true"/>
@@ -3596,7 +3650,9 @@
       <c r="K26" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="L26" s="2"/>
+      <c r="L26" t="s" s="2">
+        <v>148</v>
+      </c>
       <c r="M26" s="2"/>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -3647,7 +3703,7 @@
         <v>74</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>75</v>
@@ -3667,16 +3723,18 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E27" s="2"/>
+      <c r="E27" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="F27" t="s" s="2">
         <v>80</v>
       </c>
@@ -3693,10 +3751,12 @@
         <v>74</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>150</v>
+        <v>85</v>
       </c>
       <c r="L27" s="2"/>
-      <c r="M27" s="2"/>
+      <c r="M27" t="s" s="2">
+        <v>86</v>
+      </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -3722,13 +3782,11 @@
         <v>74</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y27" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y27" s="2"/>
       <c r="Z27" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>74</v>
@@ -3746,13 +3804,13 @@
         <v>74</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>151</v>
+        <v>89</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>74</v>
@@ -3766,21 +3824,23 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E28" s="2"/>
+      <c r="E28" t="s" s="2">
+        <v>100</v>
+      </c>
       <c r="F28" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>74</v>
@@ -3792,10 +3852,12 @@
         <v>74</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="L28" s="2"/>
-      <c r="M28" s="2"/>
+      <c r="M28" t="s" s="2">
+        <v>102</v>
+      </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -3821,11 +3883,13 @@
         <v>74</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y28" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y28" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z28" t="s" s="2">
-        <v>153</v>
+        <v>74</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>74</v>
@@ -3843,7 +3907,7 @@
         <v>74</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>154</v>
+        <v>103</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -3863,17 +3927,17 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E29" t="s" s="2">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="F29" t="s" s="2">
         <v>80</v>
@@ -3891,11 +3955,11 @@
         <v>74</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>85</v>
+        <v>106</v>
       </c>
       <c r="L29" s="2"/>
       <c r="M29" t="s" s="2">
-        <v>86</v>
+        <v>107</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -3922,11 +3986,13 @@
         <v>74</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y29" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y29" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z29" t="s" s="2">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>74</v>
@@ -3944,7 +4010,7 @@
         <v>74</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>89</v>
+        <v>108</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -3964,20 +4030,20 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E30" t="s" s="2">
-        <v>62</v>
+        <v>110</v>
       </c>
       <c r="F30" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G30" t="s" s="2">
         <v>75</v>
@@ -3992,11 +4058,13 @@
         <v>74</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="L30" s="2"/>
+        <v>111</v>
+      </c>
+      <c r="L30" t="s" s="2">
+        <v>154</v>
+      </c>
       <c r="M30" t="s" s="2">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4047,7 +4115,7 @@
         <v>74</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>158</v>
+        <v>114</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -4067,20 +4135,20 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E31" t="s" s="2">
-        <v>160</v>
+        <v>116</v>
       </c>
       <c r="F31" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G31" t="s" s="2">
         <v>75</v>
@@ -4095,11 +4163,13 @@
         <v>74</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="L31" s="2"/>
+        <v>101</v>
+      </c>
+      <c r="L31" t="s" s="2">
+        <v>157</v>
+      </c>
       <c r="M31" t="s" s="2">
-        <v>161</v>
+        <v>117</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4150,7 +4220,7 @@
         <v>74</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>162</v>
+        <v>118</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -4170,23 +4240,21 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E32" t="s" s="2">
-        <v>164</v>
-      </c>
+      <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>74</v>
@@ -4198,12 +4266,10 @@
         <v>74</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>101</v>
+        <v>159</v>
       </c>
       <c r="L32" s="2"/>
-      <c r="M32" t="s" s="2">
-        <v>165</v>
-      </c>
+      <c r="M32" s="2"/>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -4253,13 +4319,13 @@
         <v>74</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>74</v>
@@ -4273,23 +4339,21 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E33" t="s" s="2">
-        <v>168</v>
-      </c>
+      <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>74</v>
@@ -4301,12 +4365,12 @@
         <v>74</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="L33" s="2"/>
-      <c r="M33" t="s" s="2">
-        <v>169</v>
-      </c>
+        <v>126</v>
+      </c>
+      <c r="L33" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="M33" s="2"/>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -4332,13 +4396,11 @@
         <v>74</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y33" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y33" s="2"/>
       <c r="Z33" t="s" s="2">
-        <v>74</v>
+        <v>163</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>74</v>
@@ -4356,7 +4418,7 @@
         <v>74</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -4376,23 +4438,23 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E34" t="s" s="2">
-        <v>172</v>
+        <v>84</v>
       </c>
       <c r="F34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>74</v>
@@ -4404,11 +4466,11 @@
         <v>74</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="L34" s="2"/>
       <c r="M34" t="s" s="2">
-        <v>173</v>
+        <v>86</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -4435,13 +4497,11 @@
         <v>74</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y34" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y34" s="2"/>
       <c r="Z34" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>74</v>
@@ -4459,7 +4519,7 @@
         <v>74</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>174</v>
+        <v>89</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -4479,21 +4539,23 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E35" s="2"/>
+      <c r="E35" t="s" s="2">
+        <v>62</v>
+      </c>
       <c r="F35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>74</v>
@@ -4505,11 +4567,11 @@
         <v>74</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>176</v>
+        <v>85</v>
       </c>
       <c r="L35" s="2"/>
       <c r="M35" t="s" s="2">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -4560,7 +4622,7 @@
         <v>74</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -4580,21 +4642,23 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E36" s="2"/>
+      <c r="E36" t="s" s="2">
+        <v>170</v>
+      </c>
       <c r="F36" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>74</v>
@@ -4606,11 +4670,11 @@
         <v>74</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="L36" s="2"/>
       <c r="M36" t="s" s="2">
-        <v>180</v>
+        <v>171</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -4661,7 +4725,7 @@
         <v>74</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -4681,17 +4745,17 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E37" t="s" s="2">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="F37" t="s" s="2">
         <v>80</v>
@@ -4709,11 +4773,11 @@
         <v>74</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>184</v>
+        <v>101</v>
       </c>
       <c r="L37" s="2"/>
       <c r="M37" t="s" s="2">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -4764,7 +4828,7 @@
         <v>74</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -4784,17 +4848,17 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>187</v>
+        <v>177</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>187</v>
+        <v>177</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E38" t="s" s="2">
-        <v>188</v>
+        <v>178</v>
       </c>
       <c r="F38" t="s" s="2">
         <v>80</v>
@@ -4812,11 +4876,11 @@
         <v>74</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>189</v>
+        <v>101</v>
       </c>
       <c r="L38" s="2"/>
       <c r="M38" t="s" s="2">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -4867,13 +4931,13 @@
         <v>74</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>191</v>
+        <v>180</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>74</v>
@@ -4887,23 +4951,23 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>192</v>
+        <v>181</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>192</v>
+        <v>181</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E39" t="s" s="2">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="F39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>74</v>
@@ -4915,11 +4979,11 @@
         <v>74</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>194</v>
+        <v>101</v>
       </c>
       <c r="L39" s="2"/>
       <c r="M39" t="s" s="2">
-        <v>195</v>
+        <v>183</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -4970,13 +5034,13 @@
         <v>74</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>74</v>
@@ -4990,10 +5054,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5004,7 +5068,7 @@
         <v>80</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>74</v>
@@ -5016,10 +5080,12 @@
         <v>74</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="L40" s="2"/>
-      <c r="M40" s="2"/>
+      <c r="M40" t="s" s="2">
+        <v>187</v>
+      </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -5069,13 +5135,13 @@
         <v>74</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>199</v>
+        <v>188</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>74</v>
@@ -5089,10 +5155,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>200</v>
+        <v>189</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>200</v>
+        <v>189</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5103,7 +5169,7 @@
         <v>80</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>74</v>
@@ -5115,10 +5181,12 @@
         <v>74</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>201</v>
+        <v>101</v>
       </c>
       <c r="L41" s="2"/>
-      <c r="M41" s="2"/>
+      <c r="M41" t="s" s="2">
+        <v>190</v>
+      </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -5168,13 +5236,13 @@
         <v>74</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>74</v>
@@ -5188,16 +5256,18 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>203</v>
+        <v>192</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>203</v>
+        <v>192</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E42" s="2"/>
+      <c r="E42" t="s" s="2">
+        <v>193</v>
+      </c>
       <c r="F42" t="s" s="2">
         <v>80</v>
       </c>
@@ -5214,10 +5284,12 @@
         <v>74</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="L42" s="2"/>
-      <c r="M42" s="2"/>
+      <c r="M42" t="s" s="2">
+        <v>195</v>
+      </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -5267,7 +5339,7 @@
         <v>74</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -5287,21 +5359,23 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E43" s="2"/>
+      <c r="E43" t="s" s="2">
+        <v>198</v>
+      </c>
       <c r="F43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>74</v>
@@ -5313,10 +5387,12 @@
         <v>74</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="L43" s="2"/>
-      <c r="M43" s="2"/>
+      <c r="M43" t="s" s="2">
+        <v>200</v>
+      </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -5366,13 +5442,13 @@
         <v>74</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>74</v>
@@ -5386,21 +5462,23 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E44" s="2"/>
+      <c r="E44" t="s" s="2">
+        <v>203</v>
+      </c>
       <c r="F44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>74</v>
@@ -5412,10 +5490,12 @@
         <v>74</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="L44" s="2"/>
-      <c r="M44" s="2"/>
+      <c r="M44" t="s" s="2">
+        <v>205</v>
+      </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -5465,13 +5545,13 @@
         <v>74</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>74</v>
@@ -5485,10 +5565,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -5496,10 +5576,10 @@
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>74</v>
@@ -5511,9 +5591,11 @@
         <v>74</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="L45" s="2"/>
+        <v>208</v>
+      </c>
+      <c r="L45" t="s" s="2">
+        <v>209</v>
+      </c>
       <c r="M45" s="2"/>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -5564,21 +5646,522 @@
         <v>74</v>
       </c>
       <c r="AF45" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="AG45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH45" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK45" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="B46" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="C46" s="2"/>
+      <c r="D46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E46" s="2"/>
+      <c r="F46" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G46" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K46" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="L46" t="s" s="2">
         <v>213</v>
       </c>
-      <c r="AG45" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH45" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI45" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AJ45" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AK45" t="s" s="2">
+      <c r="M46" s="2"/>
+      <c r="N46" s="2"/>
+      <c r="O46" s="2"/>
+      <c r="P46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q46" s="2"/>
+      <c r="R46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF46" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="AG46" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH46" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK46" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="B47" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="C47" s="2"/>
+      <c r="D47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E47" s="2"/>
+      <c r="F47" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G47" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K47" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="L47" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="M47" s="2"/>
+      <c r="N47" s="2"/>
+      <c r="O47" s="2"/>
+      <c r="P47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q47" s="2"/>
+      <c r="R47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF47" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="AG47" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH47" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK47" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="B48" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="C48" s="2"/>
+      <c r="D48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E48" s="2"/>
+      <c r="F48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G48" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K48" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="L48" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="M48" s="2"/>
+      <c r="N48" s="2"/>
+      <c r="O48" s="2"/>
+      <c r="P48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q48" s="2"/>
+      <c r="R48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF48" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="AG48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH48" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK48" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="B49" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="C49" s="2"/>
+      <c r="D49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E49" s="2"/>
+      <c r="F49" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G49" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K49" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="L49" s="2"/>
+      <c r="M49" s="2"/>
+      <c r="N49" s="2"/>
+      <c r="O49" s="2"/>
+      <c r="P49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q49" s="2"/>
+      <c r="R49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF49" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="AG49" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH49" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK49" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="B50" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="C50" s="2"/>
+      <c r="D50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E50" s="2"/>
+      <c r="F50" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G50" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K50" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="L50" s="2"/>
+      <c r="M50" s="2"/>
+      <c r="N50" s="2"/>
+      <c r="O50" s="2"/>
+      <c r="P50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q50" s="2"/>
+      <c r="R50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF50" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="AG50" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH50" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK50" t="s" s="2">
         <v>74</v>
       </c>
     </row>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-performer.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-performer.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T11:00:40+00:00</t>
+    <t>2025-02-18T15:10:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-performer.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-performer.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:10:02+00:00</t>
+    <t>2025-02-18T15:17:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-performer.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-performer.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:17:48+00:00</t>
+    <t>2025-02-18T15:18:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-performer.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-performer.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:18:09+00:00</t>
+    <t>2025-02-18T15:18:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-performer.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-performer.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:18:38+00:00</t>
+    <t>2025-02-18T15:24:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-performer.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-performer.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:24:54+00:00</t>
+    <t>2025-02-18T15:28:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-performer.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-performer.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:28:32+00:00</t>
+    <t>2025-02-18T15:29:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-performer.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-performer.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:29:38+00:00</t>
+    <t>2025-02-18T15:30:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-performer.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-performer.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:30:04+00:00</t>
+    <t>2025-02-18T15:30:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-performer.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-performer.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:30:23+00:00</t>
+    <t>2025-02-18T15:30:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-performer.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-performer.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:30:53+00:00</t>
+    <t>2025-02-20T13:34:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-performer.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-performer.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:34:17+00:00</t>
+    <t>2025-02-20T13:46:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-performer.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-performer.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:46:00+00:00</t>
+    <t>2025-02-20T13:48:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-performer.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-performer.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:48:47+00:00</t>
+    <t>2025-02-20T13:50:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-performer.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-performer.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:50:16+00:00</t>
+    <t>2025-02-20T13:50:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-performer.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-performer.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:50:51+00:00</t>
+    <t>2025-02-20T13:51:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-performer.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-performer.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:51:52+00:00</t>
+    <t>2025-02-20T13:53:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-performer.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-performer.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:53:17+00:00</t>
+    <t>2025-02-20T13:53:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-performer.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-performer.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:53:53+00:00</t>
+    <t>2025-02-20T14:37:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-performer.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-performer.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:37:28+00:00</t>
+    <t>2025-02-20T14:38:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-performer.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-performer.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:38:00+00:00</t>
+    <t>2025-02-20T14:38:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-performer.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-performer.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:38:23+00:00</t>
+    <t>2025-02-20T14:42:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-performer.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-performer.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:42:14+00:00</t>
+    <t>2025-02-20T14:42:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-performer.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-performer.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:42:55+00:00</t>
+    <t>2025-02-20T14:43:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-performer.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-performer.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:43:30+00:00</t>
+    <t>2025-02-20T14:45:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-performer.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-performer.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:45:32+00:00</t>
+    <t>2025-02-20T14:47:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-performer.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-performer.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:47:06+00:00</t>
+    <t>2025-02-20T14:48:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-performer.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-performer.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:48:16+00:00</t>
+    <t>2025-02-20T15:31:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-performer.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-performer.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T15:31:18+00:00</t>
+    <t>2025-02-21T13:12:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-performer.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-performer.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-21T13:12:29+00:00</t>
+    <t>2025-02-21T15:18:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-performer.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-performer.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-21T15:18:09+00:00</t>
+    <t>2025-02-23T14:02:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-performer.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-performer.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-23T14:02:58+00:00</t>
+    <t>2025-02-24T10:33:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-performer.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-performer.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T10:33:29+00:00</t>
+    <t>2025-02-24T11:08:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-performer.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-performer.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T11:08:59+00:00</t>
+    <t>2025-02-24T14:08:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-performer.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-performer.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T14:08:41+00:00</t>
+    <t>2025-02-25T09:00:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
